--- a/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
+++ b/src/StaticSettingsTests/ValueRendererForBool.Test.verified.xlsx
@@ -84,10 +84,10 @@
           <t xml:space="preserve">Alice</t>
         </is>
       </c>
-      <c r="B2" s="3" t="b">
+      <c r="B2" s="3">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="b">
+      <c r="C2" s="3">
         <v>1</v>
       </c>
     </row>
@@ -97,10 +97,10 @@
           <t xml:space="preserve">Bob</t>
         </is>
       </c>
-      <c r="B3" s="3" t="b">
+      <c r="B3" s="3">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="b">
+      <c r="C3" s="3">
         <v>0</v>
       </c>
     </row>
@@ -110,7 +110,7 @@
           <t xml:space="preserve">Carol</t>
         </is>
       </c>
-      <c r="B4" s="3" t="b">
+      <c r="B4" s="3">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="inlineStr">
